--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/Sally Mugabe CH Discharge - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/Sally Mugabe CH Discharge - metadata.xlsx
@@ -485,10 +485,10 @@
         <v>form</v>
       </c>
       <c r="F2" t="str">
-        <v>NeoTreeOutcome</v>
+        <v>NeotreeOutcome</v>
       </c>
       <c r="G2" t="str">
-        <v>Outcome</v>
+        <v>Outcome at discharge</v>
       </c>
       <c r="H2" t="str">
         <v>dropdown</v>
@@ -509,7 +509,7 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>[{"value":"DC","valueLabel":"Discharged"},{"value":"NND","valueLabel":"Died"},{"value":"ABS","valueLabel":"Absconded"},{"value":"TRH","valueLabel":"Transferred to other Hospital"},{"value":"TRO","valueLabel":"Transferred to other ward"},{"value":"DAMA","valueLabel":"Discharged against medical advice"},{"value":"STB","valueLabel":"Stillbirth"},{"value":"BID","valueLabel":"Brought in dead"}]</v>
+        <v>[{"value":"DC","valueLabel":"Discharged"},{"value":"NND","valueLabel":"Died"},{"value":"ABS","valueLabel":"Absconded"},{"value":"TRH","valueLabel":"Transferred to other hospital"},{"value":"TRO","valueLabel":"Transferred to other ward"},{"value":"DAMA","valueLabel":"Discharged against medical advice"},{"value":"STB","valueLabel":"Stillbirth"},{"value":"BID","valueLabel":"Brought in dead"}]</v>
       </c>
       <c r="O2" t="str">
         <v/>
@@ -1050,7 +1050,7 @@
         <v>No</v>
       </c>
       <c r="M10" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N10" t="str">
         <v/>
@@ -1254,7 +1254,7 @@
         <v>No</v>
       </c>
       <c r="M13" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -1461,7 +1461,7 @@
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (Symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Physiological Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Suspected neonatal sepsis"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia / Bronchiolitis"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28-31 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Term with RD"},{"value":"DJ","valueLabel":"Pathological Jaundice"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"PJaundice","valueLabel":"Prolonged Jaundice"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital Dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"HIE","valueLabel":"Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Jaundice (physiological)"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Sepsis suspected"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia / Bronchiolitis"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28 to 31.6 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Respiratory Distress (term baby)"},{"value":"DJ","valueLabel":"Jaundice (pathological)"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"ProJ","valueLabel":"Jaundice (prolonged)"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Talipes MILD (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O16" t="str">
         <v>!($NeoTreeOutcome = 'BID')</v>
@@ -1931,13 +1931,13 @@
         <v>No</v>
       </c>
       <c r="L23" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M23" t="str">
-        <v>$AdmReason ! = 'DU'</v>
+        <v>$AdmReason != 'DU'</v>
       </c>
       <c r="N23" t="str">
-        <v>[{"value":"SMCH","valueLabel":"Sally Mugabe Central Hospital"},{"value":"OtH","valueLabel":"Other clinic in Harare"},{"value":"OtR","valueLabel":"Other clinic outside Harare"},{"value":"H","valueLabel":"Home"}]</v>
+        <v>[{"value":"SMCH","valueLabel":"Sally Mugabe Central Hospital"},{"value":"OthHarare","valueLabel":"Other clinic in Harare"},{"value":"OtR","valueLabel":"Other clinic outside Harare"},{"value":"H","valueLabel":"Home"},{"value":"BBA","valueLabel":"Born Before Arrival"},{"value":"Unk","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O23" t="str">
         <v>!($NeoTreeOutcome = 'BID')</v>
@@ -1984,7 +1984,7 @@
         <v>Gestation</v>
       </c>
       <c r="G24" t="str">
-        <v>Gestation at birth (weeks.days)</v>
+        <v>Estimated Gestational age at birth (weeks.days)</v>
       </c>
       <c r="H24" t="str">
         <v>number</v>
@@ -2002,7 +2002,7 @@
         <v>No</v>
       </c>
       <c r="M24" t="str">
-        <v>!($AdmReason = 'DU' or $AdmReasonAdd = 'DU')</v>
+        <v>!($AdmReason = 'DU' or [$AdmReasonAdd includes ('DU')])</v>
       </c>
       <c r="N24" t="str">
         <v/>
@@ -3229,7 +3229,7 @@
         <v/>
       </c>
       <c r="N42" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (Symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Physiological Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia / Bronchiolitis"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28-31 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"TermRD","valueLabel":"Term with RD"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"DJ","valueLabel":"Pathological Jaundice"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"PJaundice","valueLabel":"Prolonged Jaundice"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital Dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Risk factors for sepsis (but sepsis ruled out)"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"HIE","valueLabel":"Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Jaundice (physiological)"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia / Bronchiolitis"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28 to 31.6 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"TermRD","valueLabel":"Respiratory Distress (term baby)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"DJ","valueLabel":"Jaundice (pathological)"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"ProJ","valueLabel":"Jaundice (prolonged)"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Talipes MILD (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Sepsis (risk factors, but ruled out)"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O42" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome =  'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO'</v>
@@ -3501,7 +3501,7 @@
         <v/>
       </c>
       <c r="N46" t="str">
-        <v>[{"value":"Safe","valueLabel":"Safekeeping"},{"value":"ExPrem","valueLabel":"Extremely premature (&lt;28 weeks)"},{"value":"VPrem","valueLabel":"Very premature (28-31 weeks)"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"LBW","valueLabel":"Low birth weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very low birth weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"EOS","valueLabel":"Suspected neonatal sepsis within first 48 hours (EONS)"},{"value":"LOS","valueLabel":"Suspected neonatal sepsis after first 48 hours (LONS)"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"ConSep","valueLabel":"Confirmed sepsis (blood culture positive)"},{"value":"sHIE","valueLabel":"Suspected hypoxic ischaemic encephalopathy"},{"value":"BA","valueLabel":"Hypoxic ischaemic encephalopathy"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"MecEx","valueLabel":"Born through meconium"},{"value":"MecAsp","valueLabel":"Suspected Meconium aspiration syndrome"},{"value":"TTN","valueLabel":"Transient tachypnoea of newborn (TTN)"},{"value":"RD","valueLabel":"Respiratory distress"},{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital abnormalities"},{"value":"CHD","valueLabel":"Possible congenital heart disease"},{"value":"Conv","valueLabel":"Convulsions/Seizures"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty Feeding"},{"value":"NTF","valueLabel":"Not tolerating feeds"},{"value":"Wt","valueLabel":"Poor weight gain"},{"value":"Fd","valueLabel":"Establishing feeding"},{"value":"LBM","valueLabel":"Hypoglycaemia"},{"value":"Wtloss","valueLabel":"More than 10% weight loss from birth weight"},{"value":"Run","valueLabel":"Runny nose/snuffly"},{"value":"Cou","valueLabel":"Cough"},{"value":"Oxyreq","valueLabel":"Oxygen requirement/low saturations"},{"value":"Fev","valueLabel":"Fever"},{"value":"Vom","valueLabel":"Vomitting"},{"value":"NBO","valueLabel":"Not opening bowels"},{"value":"Leth","valueLabel":"Lethargic/more sleepy"},{"value":"IncCry","valueLabel":"Increased crying/irritability"},{"value":"Pn","valueLabel":"Pain"},{"value":"AbdDis","valueLabel":"Abdominal distention"},{"value":"Wnd","valueLabel":"Wound break down"},{"value":"IncHC","valueLabel":"Increasing head circumference"},{"value":"Bld","valueLabel":"Bleeding"},{"value":"Pal","valueLabel":"Pallor"},{"value":"NewJ","valueLabel":"Jaundice"},{"value":"Phx","valueLabel":"On phototherapy treatment"},{"value":"Rash","valueLabel":"Rash"},{"value":"Wtloss","valueLabel":"Loosing weight/inadequate weight gain"},{"value":"Parcon","valueLabel":"Parental concern"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"Syp","valueLabel":"Syphilis exposed"},{"value":"SSyp","valueLabel":"Suspected congenital syphilis infection"},{"value":"J","valueLabel":"Jaundice"},{"value":"Hypo","valueLabel":"Hypothermia"},{"value":"PN","valueLabel":"Pneumonia/bronchiolitis"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftLipPalate","valueLabel":"Cleft Palate"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"GSchred","valueLabel":"Gastroschisis reduction in progress"},{"value":"GSchcom","valueLabel":"Gastroschisis reduction completed"},{"value":"Stoma","valueLabel":"Stoma"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"NEC","valueLabel":"Suspected necrotising enterocolitis (NEC)"},{"value":"MyeloO","valueLabel":"Myelomeningocele Open"},{"value":"MyeloC","valueLabel":"Myelomeningocele Closed"},{"value":"MyeloI","valueLabel":"Myelomeningocele infected"},{"value":"Myelopost","valueLabel":"Myelomeningocele post surgery"},{"value":"Gen","valueLabel":"Suspected genetic abnormality/syndrome"},{"value":"HydCeph","valueLabel":"Hydrocephalus"},{"value":"HydCephVP","valueLabel":"Hydrocephalus with VP shunt inserted"},{"value":"Abs","valueLabel":"Abscess"},{"value":"CDH","valueLabel":"Congenital dislocation of the hip"},{"value":"MiTalipes","valueLabel":"Mild talipes (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate to severe Talipes (club foot)"},{"value":"Safeguard","valueLabel":"Safeguarding concern"},{"value":"other","valueLabel":"Other"}]</v>
+        <v>[{"value":"Safe","valueLabel":"Safekeeping"},{"value":"ExPrem","valueLabel":"Extremely premature (&lt;28 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28 to 31.6 weeks)"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"LBW","valueLabel":"Low birth weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very low birth weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"Extremely low birth weight (&lt;1000g)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"EOS","valueLabel":"Suspected neonatal sepsis within first 48 hours (EONS)"},{"value":"LOS","valueLabel":"Suspected neonatal sepsis after first 48 hours (LONS)"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"ConSep","valueLabel":"Confirmed sepsis (blood culture positive)"},{"value":"sHIE","valueLabel":"Suspected hypoxic ischaemic encephalopathy"},{"value":"HIE","valueLabel":"Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"MecEx","valueLabel":"Born through meconium"},{"value":"MecAsp","valueLabel":"Suspected Meconium aspiration syndrome"},{"value":"TTN","valueLabel":"Transient tachypnoea of newborn (TTN)"},{"value":"RD","valueLabel":"Respiratory distress"},{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital abnormalities"},{"value":"CHD","valueLabel":"Possible congenital heart disease"},{"value":"Conv","valueLabel":"Convulsions/Seizures"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty Feeding"},{"value":"NTF","valueLabel":"Not tolerating feeds"},{"value":"Wt","valueLabel":"Poor weight gain"},{"value":"Fd","valueLabel":"Establishing feeding"},{"value":"LBM","valueLabel":"Hypoglycaemia"},{"value":"Wtloss","valueLabel":"More than 10% weight loss from birth weight"},{"value":"Run","valueLabel":"Runny nose/snuffly"},{"value":"Cou","valueLabel":"Cough"},{"value":"Oxyreq","valueLabel":"Oxygen requirement/low saturations"},{"value":"Fev","valueLabel":"Fever"},{"value":"Vom","valueLabel":"Vomitting"},{"value":"NBO","valueLabel":"Not passing stool"},{"value":"Leth","valueLabel":"Lethargic/more sleepy"},{"value":"IncCry","valueLabel":"Increased crying/irritability"},{"value":"Pn","valueLabel":"Pain"},{"value":"AbdDis","valueLabel":"Abdominal distention"},{"value":"Wnd","valueLabel":"Wound break down"},{"value":"IncHC","valueLabel":"Increasing head circumference"},{"value":"Bld","valueLabel":"Bleeding"},{"value":"Pal","valueLabel":"Pallor"},{"value":"NewJ","valueLabel":"Jaundice"},{"value":"Phx","valueLabel":"On phototherapy treatment"},{"value":"Rash","valueLabel":"Rash"},{"value":"Wtloss","valueLabel":"Loosing weight/inadequate weight gain"},{"value":"Parcon","valueLabel":"Parental concern"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"Syp","valueLabel":"Syphilis exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"Hypo","valueLabel":"Hypothermia"},{"value":"PN","valueLabel":"Pneumonia/bronchiolitis"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftLipPalate","valueLabel":"Cleft Palate"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"GSchred","valueLabel":"Gastroschisis reduction in progress"},{"value":"GSchcom","valueLabel":"Gastroschisis reduction completed"},{"value":"Stoma","valueLabel":"Stoma"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"NEC","valueLabel":"Necrotising enterocolitis (consider)"},{"value":"MyeloO","valueLabel":"Myelomeningocele Open"},{"value":"MyeloC","valueLabel":"Myelomeningocele Closed"},{"value":"MyeloI","valueLabel":"Myelomeningocele infected"},{"value":"Myelopost","valueLabel":"Myelomeningocele post surgery"},{"value":"Gen","valueLabel":"Suspected genetic abnormality/syndrome"},{"value":"HydCeph","valueLabel":"Hydrocephalus"},{"value":"HydCephVP","valueLabel":"Hydrocephalus with VP shunt inserted"},{"value":"Abs","valueLabel":"Abscess"},{"value":"CDH","valueLabel":"Congenital dislocation of the hip"},{"value":"MiTalipes","valueLabel":"Talipes MILD (club foot)"},{"value":"MoTalipes","valueLabel":"Talipes MODERATE (club foot)"},{"value":"Safeguard","valueLabel":"Safeguarding concern"},{"value":"other","valueLabel":"Other"}]</v>
       </c>
       <c r="O46" t="str">
         <v>$DRU = true</v>
@@ -3977,7 +3977,7 @@
         <v/>
       </c>
       <c r="N53" t="str">
-        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Dumped baby"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (Symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"BA","valueLabel":"Hypoxic Ischaemic Encephalopathy"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Physiological Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia / Bronchiolitis"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28-31 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Term with RD"},{"value":"DJ","valueLabel":"Pathological Jaundice"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"PJaundice","valueLabel":"Prolonged Jaundice"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital Dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Mild Talipes (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"An","valueLabel":"Anaemia"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BI","valueLabel":"Birth Trauma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CHD","valueLabel":"Consider Congenital Heart Disease"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty feeding"},{"value":"DUM","valueLabel":"Abandoned baby"},{"value":"HIVLR","valueLabel":"HIV low risk"},{"value":"HIVHR","valueLabel":"HIV high risk"},{"value":"HIVU","valueLabel":"HIV unknown"},{"value":"HypogAs","valueLabel":"Hypoglycaemia (NOT symptomatic)"},{"value":"HypogSy","valueLabel":"Hypoglycaemia (symptomatic)"},{"value":"RiHypog","valueLabel":"Risk of hypoglycaemia"},{"value":"HIE","valueLabel":"Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"MJ","valueLabel":"Jaundice (physiological)"},{"value":"LBW","valueLabel":"Low Birth Weight (1500-2499g)"},{"value":"VLBW","valueLabel":"Very Low Birth Weight (1000-1499g)"},{"value":"ExLBW","valueLabel":"ExtremelyLow Birth Weight (&lt;1000g)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MecEx","valueLabel":"Meconium exposure (asymptomatic baby)"},{"value":"MiHypo","valueLabel":"Mild Hypothermia"},{"value":"ModHypo","valueLabel":"Moderate Hypothermia"},{"value":"SHypo","valueLabel":"Severe Hypothermia"},{"value":"Hyperth","valueLabel":"Hyperthermia"},{"value":"NB","valueLabel":"Normal baby"},{"value":"PN","valueLabel":"Pneumonia / Bronchiolitis"},{"value":"Prem","valueLabel":"Premature (32-36 weeks)"},{"value":"VPrem","valueLabel":"Very Premature (28 to 31.6 weeks)"},{"value":"ExPrem","valueLabel":"Extremely Premature (&lt;28 weeks)"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"TermRD","valueLabel":"Respiratory Distress (term baby)"},{"value":"DJ","valueLabel":"Jaundice (pathological)"},{"value":"sHIE","valueLabel":"Suspected Hypoxic Ischaemic Encephalopathy"},{"value":"ProJ","valueLabel":"Jaundice (prolonged)"},{"value":"CleftLip","valueLabel":"Cleft lip"},{"value":"CleftRD","valueLabel":"Cleft lip and/or palate with RD"},{"value":"CleftLipPalate","valueLabel":"Cleft lip and/or palate"},{"value":"Omph","valueLabel":"Omphalocele"},{"value":"Myelo","valueLabel":"Myelomeningocele"},{"value":"CDH","valueLabel":"Congenital dislocation of the hip (CDH)"},{"value":"MiTalipes","valueLabel":"Talipes MILD (club foot)"},{"value":"MoTalipes","valueLabel":"Moderate Talipes (club foot)"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O53" t="str">
         <v>$NeoTreeOutcome = 'NND' or $NeoTreeOutcome = 'DDA'</v>
@@ -5337,7 +5337,7 @@
         <v>$BC = true</v>
       </c>
       <c r="N73" t="str">
-        <v>[{"value":"NO","valueLabel":"No Growth"},{"value":"CO","valueLabel":"Likely Contaminant Organism"},{"value":"BS","valueLabel":"Bacillus Sp"},{"value":"CONS","valueLabel":"Coagulase Negative Staphylococcus"},{"value":"EC","valueLabel":"E.Coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"GDS","valueLabel":"Group D Streptococcus"},{"value":"KP","valueLabel":"Klebsiella Pneumoniae"},{"value":"PA","valueLabel":"Pseudomonas Aeruginosa"},{"value":"SA","valueLabel":"Staphylococcus Aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose Fermenting Coliform"},{"value":"OGN","valueLabel":"Other Gram Negative"},{"value":"OGP","valueLabel":"Other Gram Positive"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"NO","valueLabel":"No Growth"},{"value":"CO","valueLabel":"Likely Contaminant Organism"},{"value":"BS","valueLabel":"Bacillus Sp"},{"value":"CONS","valueLabel":"Coagulase Negative Staphylococcus"},{"value":"EC","valueLabel":"E.Coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"GDS","valueLabel":"Group D Streptococcus"},{"value":"SA","valueLabel":"Staphylococcus Aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose Fermenting Coliform"},{"value":"OGN","valueLabel":"Other Gram Negative"},{"value":"OGP","valueLabel":"Other Gram Positive"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O73" t="str">
         <v>$FBC = true or $CRP = true or $BC = true or $UE = true or $Bili = true or $TORCH = true or $Bone = true or $GLUC = true or $HIVPCRInf = true or $MatRPR = true or $MatHIVP = true</v>
@@ -8057,7 +8057,7 @@
         <v>$BC2 = true</v>
       </c>
       <c r="N113" t="str">
-        <v>[{"value":"NO","valueLabel":"No Organisms"},{"value":"CO","valueLabel":"Likely Contaminant Organism"},{"value":"BS","valueLabel":"Bacillus sp."},{"value":"CONS","valueLabel":"Coagulase negative staphylococcus"},{"value":"EC","valueLabel":"E.Coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"KP","valueLabel":"Klabsiella Pneumoniae"},{"value":"PA","valueLabel":"Pseudomonas Aeruginosa"},{"value":"SA","valueLabel":"Staphylococcus Aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose Fermenting Coliform"},{"value":"OGN","valueLabel":"Other Gram Negative"},{"value":"OGP","valueLabel":"Other Gram Positive"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"NO","valueLabel":"No Organisms"},{"value":"CO","valueLabel":"Likely Contaminant Organism"},{"value":"BS","valueLabel":"Bacillus sp."},{"value":"CONS","valueLabel":"Coagulase negative staphylococcus"},{"value":"EC","valueLabel":"E.Coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"KP","valueLabel":"Klabsiella Pneumoniae"},{"value":"SA","valueLabel":"Staphylococcus Aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose Fermenting Coliform"},{"value":"OGN","valueLabel":"Other Gram Negative"},{"value":"OGP","valueLabel":"Other Gram Positive"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O113" t="str">
         <v>$FBC2 = true or $CRP2 = true or $BC2 = true or $UE2 = true or $Bili2 = true or $Bone2 = true or $GLUC2 = true</v>
@@ -9621,7 +9621,7 @@
         <v>$LP = 'YesP'</v>
       </c>
       <c r="N136" t="str">
-        <v>[{"value":"CO","valueLabel":"Likely contaminant organism"},{"value":"BS","valueLabel":"Bacillus sp"},{"value":"CONS","valueLabel":"Coagulase negative staphylococcus"},{"value":"EC","valueLabel":"E. coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"GDS","valueLabel":"Group D Streptococcus"},{"value":"KP","valueLabel":"Klebsiella pneumoniae"},{"value":"PA","valueLabel":"Pseudomonas aeruginosa"},{"value":"SA","valueLabel":"Staphylococcus aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose fermenting coliform"},{"value":"TB","valueLabel":"Mycobacterium tuberculosis"},{"value":"OGN","valueLabel":"Other Gram negative"},{"value":"OGP","valueLabel":"Other Gram positive"}]</v>
+        <v>[{"value":"CO","valueLabel":"Likely contaminant organism"},{"value":"BS","valueLabel":"Bacillus sp"},{"value":"CONS","valueLabel":"Coagulase negative staphylococcus"},{"value":"EC","valueLabel":"E. coli"},{"value":"GBS","valueLabel":"Group B Streptococcus"},{"value":"GDS","valueLabel":"Group D Streptococcus"},{"value":"SA","valueLabel":"Staphylococcus aureus"},{"value":"LFC","valueLabel":"Lactose Fermenting Coliform"},{"value":"NLFC","valueLabel":"Non Lactose fermenting coliform"},{"value":"TB","valueLabel":"Mycobacterium tuberculosis"},{"value":"OGN","valueLabel":"Other Gram negative"},{"value":"OGP","valueLabel":"Other Gram positive"}]</v>
       </c>
       <c r="O136" t="str">
         <v>$LP = 'YesN' or $LP = 'YesP'</v>
@@ -11501,10 +11501,10 @@
         <v>form</v>
       </c>
       <c r="F164" t="str">
-        <v>HAART</v>
+        <v>MaHAART</v>
       </c>
       <c r="G164" t="str">
-        <v>Maternal HAART Status</v>
+        <v>Is the mother on HAART?</v>
       </c>
       <c r="H164" t="str">
         <v>dropdown</v>
@@ -15611,7 +15611,7 @@
         <v>$SPECREV = 'Y'</v>
       </c>
       <c r="N224" t="str">
-        <v>[{"value":"PaedSurg","valueLabel":"Paediatric Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Neph","valueLabel":"Nephrology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ortho","valueLabel":"Orthopaedic Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Opth","valueLabel":"Opthalmology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MxFx","valueLabel":"Maxillofacial Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Neuro","valueLabel":"Neurology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Endoc","valueLabel":"Endocrinology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Oth","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"PaedSurg","valueLabel":"Paediatric Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Neph","valueLabel":"Nephrology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ortho","valueLabel":"Orthopaedic Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Opth","valueLabel":"Opthalmology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MxFx","valueLabel":"Maxillofacial Surgery","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Endoc","valueLabel":"Endocrinology","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Oth","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O224" t="str">
         <v>$SPECREV = 'Y'</v>
@@ -16814,7 +16814,7 @@
         <v>Gestation</v>
       </c>
       <c r="G242" t="str">
-        <v>Gestation (weeks.days)</v>
+        <v>Estimated Gestational age at birth (weeks.days)</v>
       </c>
       <c r="H242" t="str">
         <v>number</v>
@@ -17855,7 +17855,7 @@
         <v/>
       </c>
       <c r="N257" t="str">
-        <v>[{"value":"A","valueLabel":"African"},{"value":"AA","valueLabel":"African/AfricanAmerican"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"A","valueLabel":"African"},{"value":"AS","valueLabel":"Asian/Pacific Islander"},{"value":"W","valueLabel":"White"},{"value":"NA","valueLabel":"NativeAmerican"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O257" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -19487,7 +19487,7 @@
         <v>$NeoTreeOutcome = 'BID'</v>
       </c>
       <c r="N281" t="str">
-        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"PROM","valueLabel":"PROM more than 18 hrs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MF","valueLabel":"Maternal fever in labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OL","valueLabel":"Offensive Liquor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pr2nd","valueLabel":"Prolonged second stage labour","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born Before Arrival (BBA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Prem","valueLabel":"Prematurity &lt; 37 weeks","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O281" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -20969,7 +20969,7 @@
         <v>REVCLINTYP</v>
       </c>
       <c r="G303" t="str">
-        <v>If yes which clinic?</v>
+        <v>Review Clinic</v>
       </c>
       <c r="H303" t="str">
         <v>dropdown</v>
@@ -20990,7 +20990,7 @@
         <v>$REVCLIN = 'Y'</v>
       </c>
       <c r="N303" t="str">
-        <v>[{"value":"KMC","valueLabel":"Kangaroo clinic (Thursday)"},{"value":"NNC","valueLabel":"Neonatal clinic (Friday)"},{"value":"LOC","valueLabel":"Local clinic"},{"value":"SUR","valueLabel":"Surgical clinic"},{"value":"ORTH","valueLabel":"Orthopaedic clinic"},{"value":"PC","valueLabel":"Plastics Clinic"},{"value":"MFC","valueLabel":"Maxillofacial Clinic"},{"value":"NSC","valueLabel":"Neuro Surgery Clinic"},{"value":"OTH","valueLabel":"Other clinic"}]</v>
+        <v>[{"value":"KMC","valueLabel":"Kangaroo clinic (Thursday)"},{"value":"NNC","valueLabel":"Neonatal clinic (Friday)"},{"value":"LOC","valueLabel":"Local clinic"},{"value":"SUR","valueLabel":"Surgical clinic"},{"value":"ORTH","valueLabel":"Orthopaedic clinic"},{"value":"PC","valueLabel":"Plastics Clinic"},{"value":"MFC","valueLabel":"Maxillofacial Clinic"},{"value":"OTH","valueLabel":"Other clinic"}]</v>
       </c>
       <c r="O303" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO'</v>
